--- a/data/processed/model_avg_F1.xlsx
+++ b/data/processed/model_avg_F1.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7927866083819691</v>
+        <v>0.792786609835741</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8840566699097796</v>
+        <v>0.8840566713635515</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8780193285244268</v>
+        <v>0.8780193270706549</v>
       </c>
     </row>
     <row r="9">

--- a/data/processed/model_avg_F1.xlsx
+++ b/data/processed/model_avg_F1.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8868817090988159</v>
+        <v>0.8868817061912723</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8846564118455096</v>
+        <v>0.8846564103917378</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8840566713635515</v>
+        <v>0.8840566742710951</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5549715815520868</v>
+        <v>0.5549715800983149</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/model_avg_F1.xlsx
+++ b/data/processed/model_avg_F1.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8868817061912723</v>
+        <v>0.8868817076450441</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8846564103917378</v>
+        <v>0.8846564089379659</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.792786609835741</v>
+        <v>0.7927866083819691</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8840566742710951</v>
+        <v>0.8840566728173233</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8780193270706549</v>
+        <v>0.8780193285244268</v>
       </c>
     </row>
     <row r="9">
